--- a/data_flows.xlsx
+++ b/data_flows.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>原始事件流水</t>
+          <t>Raw event logs</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -526,6 +526,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>OutputFields</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alias</t>
         </is>
       </c>
     </row>
@@ -540,6 +545,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -554,168 +560,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TargetTable</t>
+          <t>TargetField</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TargetField</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>raw_events</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>stg_events</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>uid</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>直接映射</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>raw_events</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>event_time</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>stg_events</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>event_ts</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>to_timestamp()</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>时间格式化</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>raw_events</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>page_url</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>stg_events</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>urldecode</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>raw_events</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>dw_order_fact</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>直接映射</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>raw_events</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>dw_order_fact</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>直接映射</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -728,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,7 +628,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>清洗后事件表</t>
+          <t>Staging events</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -834,6 +691,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>OutputFields</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alias</t>
         </is>
       </c>
     </row>
@@ -866,6 +728,7 @@
           <t>user_id, event_time, page_url</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -878,7 +741,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>raw_events</t>
+          <t>(previous)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -892,6 +755,7 @@
           <t>uid AS user_id, to_timestamp(event_time) AS event_ts, url_decode(page_url) AS url</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -906,20 +770,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TargetTable</t>
+          <t>TargetField</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TargetField</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -938,20 +797,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>stg_events</t>
+          <t>uid</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>uid</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>直接映射</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>Direct mapping</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -966,22 +820,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>stg_events</t>
+          <t>event_ts</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>event_ts</t>
+          <t>to_timestamp()</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>to_timestamp()</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>时间格式化</t>
+          <t>Time formatting</t>
         </is>
       </c>
     </row>
@@ -998,172 +847,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>stg_events</t>
+          <t>url</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>urldecode</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>stg_events</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>uid</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>dim_user</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>UPSERT</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>新用户插入，老用户更新最后活跃时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>stg_events</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>dim_user</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>last_page</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LAST_VALUE(url) OVER (PARTITION BY uid ORDER BY event_ts)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>stg_events</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>uid</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>dw_user_agg</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>JOIN key</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>stg_events</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>event_ts</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>dw_user_agg</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>last_event_time</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MAX(event_ts)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>聚合</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>stg_events</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>dw_user_agg</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>last_url</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAST_VALUE(url) OVER (PARTITION BY uid ORDER BY event_ts)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>窗口函数</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1176,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1219,7 +911,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>用户维度表</t>
+          <t>User dimension</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1282,6 +974,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>OutputFields</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alias</t>
         </is>
       </c>
     </row>
@@ -1296,6 +993,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1310,20 +1008,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TargetTable</t>
+          <t>TargetField</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TargetField</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1342,22 +1035,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dim_user</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>UPSERT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UPSERT</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>新用户插入，老用户更新最后活跃时间</t>
+          <t>New user insert, update last active time</t>
         </is>
       </c>
     </row>
@@ -1374,80 +1062,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dim_user</t>
+          <t>last_page</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>last_page</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
           <t>LAST_VALUE(url) OVER (PARTITION BY uid ORDER BY event_ts)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>dim_user</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>dw_user_agg</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>直接映射</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>来自维度表</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>dim_user</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>dw_user_agg</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>直接映射</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1460,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1503,7 +1126,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>用户聚合宽表</t>
+          <t>User aggregated wide table</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1566,6 +1189,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>OutputFields</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alias</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1203,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JOIN</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1583,31 +1211,20 @@
           <t>stg_events</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>dim_user</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LEFT</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>stg_events.uid = dim_user.user_id</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stg_events.event_ts IS NOT NULL</t>
+          <t>event_ts IS NOT NULL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stg_events.uid, dim_user.user_name, dim_user.city, stg_events.event_ts, stg_events.url</t>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>filtered_events</t>
         </is>
       </c>
     </row>
@@ -1617,27 +1234,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WINDOW</t>
+          <t>JOIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(previous)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>(alias filtered_events)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dim_user</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>filtered_events.uid = dim_user.user_id</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>ROW_NUMBER() OVER (PARTITION BY uid ORDER BY event_ts DESC) AS rn</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>*, rn</t>
+          <t>filtered_events.uid, dim_user.user_name, dim_user.city, filtered_events.event_ts, filtered_events.url</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>joined_user</t>
         </is>
       </c>
     </row>
@@ -1647,121 +1277,115 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>WINDOW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(previous)</t>
+          <t>(alias joined_user)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>rn = 1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ROW_NUMBER() OVER (PARTITION BY uid ORDER BY event_ts DESC) AS rn</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
+          <t>*, rn</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ranked</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FILTER</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(alias ranked)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>rn = 1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>uid, user_name, city, event_ts AS last_event_time, url AS last_url</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SourceTable</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>SourceField</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TargetTable</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TargetField</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stg_events</t>
+          <t>SourceTable</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>uid</t>
+          <t>SourceField</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dw_user_agg</t>
+          <t>TargetField</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>user_id</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JOIN key</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dim_user</t>
+          <t>stg_events</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_name</t>
+          <t>uid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dw_user_agg</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>直接映射</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>来自维度表</t>
-        </is>
-      </c>
+          <t>JOIN key</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1771,57 +1395,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dw_user_agg</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>Direct mapping</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>直接映射</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>From dimension table</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stg_events</t>
+          <t>dim_user</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_ts</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dw_user_agg</t>
+          <t>city</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>last_event_time</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MAX(event_ts)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>聚合</t>
-        </is>
-      </c>
+          <t>Direct mapping</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1831,91 +1445,49 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>event_ts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dw_user_agg</t>
+          <t>last_event_time</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>last_url</t>
+          <t>MAX(event_ts)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAST_VALUE(url) OVER (PARTITION BY uid ORDER BY event_ts)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>窗口函数</t>
+          <t>Aggregation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dw_user_agg</t>
+          <t>stg_events</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>last_event_time</t>
+          <t>url</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>report_daily</t>
+          <t>last_url</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>dt</t>
+          <t>LAST_VALUE(url) OVER (PARTITION BY uid ORDER BY event_ts)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>date_trunc('day', last_event_time)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>截取日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dw_user_agg</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>report_daily</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>user_count</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>COUNT(DISTINCT user_id)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>聚合</t>
+          <t>Window function</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1973,7 +1545,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>日报表</t>
+          <t>Daily report</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2036,6 +1608,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>OutputFields</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alias</t>
         </is>
       </c>
     </row>
@@ -2064,6 +1641,7 @@
           <t>dt, COUNT(DISTINCT user_id) AS user_count</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2078,20 +1656,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TargetTable</t>
+          <t>TargetField</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TargetField</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2110,22 +1683,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>report_daily</t>
+          <t>dt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dt</t>
+          <t>date_trunc('day', last_event_time)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>date_trunc('day', last_event_time)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>截取日期</t>
+          <t>Date truncation</t>
         </is>
       </c>
     </row>
@@ -2142,22 +1710,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>report_daily</t>
+          <t>user_count</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>user_count</t>
+          <t>COUNT(DISTINCT user_id)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>COUNT(DISTINCT user_id)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>聚合</t>
+          <t>Aggregation</t>
         </is>
       </c>
     </row>
@@ -2172,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2215,7 +1778,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>产品维度表</t>
+          <t>Product dimension</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2278,6 +1841,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>OutputFields</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alias</t>
         </is>
       </c>
     </row>
@@ -2292,6 +1860,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2306,52 +1875,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TargetTable</t>
+          <t>TargetField</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TargetField</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dim_product</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>product_name</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>dw_order_fact</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>product_name</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>JOIN 取得</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2364,7 +1900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2407,7 +1943,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>订单事实表</t>
+          <t>Order fact table</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2470,6 +2006,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>OutputFields</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alias</t>
         </is>
       </c>
     </row>
@@ -2510,66 +2051,65 @@
           <t>order_id, product_id, product_name</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SourceTable</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SourceField</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TargetTable</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TargetField</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>order_with_product</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FILTER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(alias order_with_product)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>order_id IS NOT NULL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>raw_events</t>
+          <t>SourceTable</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>order_id</t>
+          <t>SourceField</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dw_order_fact</t>
+          <t>TargetField</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>order_id</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>直接映射</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2579,81 +2119,66 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>product_id</t>
+          <t>order_id</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dw_order_fact</t>
+          <t>order_id</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>直接映射</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>Direct mapping</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dim_product</t>
+          <t>raw_events</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>product_name</t>
+          <t>product_id</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dw_order_fact</t>
+          <t>product_id</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>product_name</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>JOIN 取得</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>Direct mapping</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dw_order_fact</t>
+          <t>dim_product</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>order_id</t>
+          <t>product_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>report_monthly</t>
+          <t>product_name</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>order_count</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>COUNT(order_id)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>JOIN obtained</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2666,7 +2191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2709,7 +2234,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>月报表</t>
+          <t>Monthly report</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2772,6 +2297,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>OutputFields</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Alias</t>
         </is>
       </c>
     </row>
@@ -2800,6 +2330,7 @@
           <t>event_month, COUNT(order_id) AS order_count</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2814,20 +2345,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TargetTable</t>
+          <t>TargetField</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TargetField</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2846,20 +2372,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>report_monthly</t>
+          <t>order_count</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>order_count</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>COUNT(order_id)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
